--- a/artfynd/A 41262-2023 artfynd.xlsx
+++ b/artfynd/A 41262-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41262-2023 artfynd.xlsx
+++ b/artfynd/A 41262-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66635489</v>
+        <v>66635412</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590446.0977990128</v>
+        <v>590617</v>
       </c>
       <c r="R2" t="n">
-        <v>6612140.805602393</v>
+        <v>6612151</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2017-05-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66635412</v>
+        <v>66635416</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590617.1251724216</v>
+        <v>590320</v>
       </c>
       <c r="R3" t="n">
-        <v>6612151.012477284</v>
+        <v>6612211</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +848,9 @@
           <t>2017-05-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66635416</v>
+        <v>66635422</v>
       </c>
       <c r="B4" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590319.74636875</v>
+        <v>590568</v>
       </c>
       <c r="R4" t="n">
-        <v>6612211.103150316</v>
+        <v>6612249</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,19 +949,9 @@
           <t>2017-05-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66635422</v>
+        <v>95827867</v>
       </c>
       <c r="B5" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,9 +1006,10 @@
           <t>(Bechstein, 1793)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,13 +1018,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590568.1357819634</v>
+        <v>590415</v>
       </c>
       <c r="R5" t="n">
-        <v>6612248.973497312</v>
+        <v>6612254</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,12 +1068,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1142,12 +1083,7 @@
         <v>95827868</v>
       </c>
       <c r="B6" t="n">
-        <v>57539</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,43 +1182,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95827867</v>
+        <v>66635456</v>
       </c>
       <c r="B7" t="n">
-        <v>57539</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1291,13 +1221,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590415</v>
+        <v>590233</v>
       </c>
       <c r="R7" t="n">
-        <v>6612254</v>
+        <v>6612339</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Rebecka Le Moine</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Rebecka Le Moine</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1356,12 +1286,7 @@
         <v>95827869</v>
       </c>
       <c r="B8" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590232.366240705</v>
+        <v>590232</v>
       </c>
       <c r="R8" t="n">
-        <v>6612388.566928614</v>
+        <v>6612389</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1431,19 +1356,9 @@
           <t>2021-05-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-05-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,6 +1382,107 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66635489</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finnslätten, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590446</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6612141</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41262-2023 artfynd.xlsx
+++ b/artfynd/A 41262-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66635412</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66635416</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66635422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95827867</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95827868</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66635456</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95827869</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,8 +1523,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66635489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>